--- a/backend/uploads/importacao-relatorio/entradas_lojas.xlsx
+++ b/backend/uploads/importacao-relatorio/entradas_lojas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR272"/>
+  <dimension ref="A1:BR271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74721,12 +74721,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>310591</t>
+          <t>310670</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
+          <t>761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -74734,46 +74734,46 @@
       <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>4.818</t>
+          <t>685.430</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="I268" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="J268" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>XML</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>1217.1</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H268" s="2" t="n">
-        <v>46209</v>
-      </c>
-      <c r="I268" s="2" t="n">
-        <v>46211</v>
-      </c>
-      <c r="J268" s="2" t="n">
-        <v>46240</v>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>XML</t>
-        </is>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>3789.95</t>
-        </is>
-      </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>3789.95</t>
+          <t>1217.1</t>
         </is>
       </c>
       <c r="P268" t="inlineStr">
@@ -74783,12 +74783,12 @@
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>0.00558</t>
+          <t>0.00247</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="S268" t="inlineStr">
@@ -74798,7 +74798,7 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>3.789,95</t>
+          <t>1.217,10</t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
@@ -74808,12 +74808,12 @@
       </c>
       <c r="V268" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1027.2</t>
         </is>
       </c>
       <c r="W268" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="X268" t="inlineStr">
@@ -74823,12 +74823,12 @@
       </c>
       <c r="Y268" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -74838,7 +74838,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="AC268" t="inlineStr">
@@ -74848,12 +74848,12 @@
       </c>
       <c r="AD268" t="inlineStr">
         <is>
-          <t>3789.95</t>
+          <t>1217.1</t>
         </is>
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>151.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -74980,7 +74980,7 @@
       <c r="BM268" t="inlineStr"/>
       <c r="BN268" t="inlineStr">
         <is>
-          <t>52260705104359000122550010000048181870606619</t>
+          <t>42260775339051000141550080006854301622675457</t>
         </is>
       </c>
       <c r="BO268" t="inlineStr"/>
@@ -74999,12 +74999,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>310672</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+          <t>21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -75012,12 +75012,12 @@
       <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>685.430</t>
+          <t>116.922</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H269" s="2" t="n">
@@ -75036,7 +75036,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>1217.1</t>
+          <t>8562.49</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -75046,12 +75046,12 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>1217.1</t>
+          <t>7991.52</t>
         </is>
       </c>
       <c r="P269" t="inlineStr">
@@ -75061,12 +75061,12 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>0.00247</t>
+          <t>0.049824</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -75076,7 +75076,7 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>1.217,10</t>
+          <t>8.562,49</t>
         </is>
       </c>
       <c r="U269" t="inlineStr">
@@ -75086,12 +75086,12 @@
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>1027.2</t>
+          <t>6962.21</t>
         </is>
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="X269" t="inlineStr">
@@ -75101,12 +75101,12 @@
       </c>
       <c r="Y269" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>62.66</t>
         </is>
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>54.13</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -75121,17 +75121,17 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>570.97</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
         <is>
-          <t>1217.1</t>
+          <t>7991.52</t>
         </is>
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>319.66</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -75258,7 +75258,7 @@
       <c r="BM269" t="inlineStr"/>
       <c r="BN269" t="inlineStr">
         <is>
-          <t>42260775339051000141550080006854301622675457</t>
+          <t>42260735635346000140550020001169221345408115</t>
         </is>
       </c>
       <c r="BO269" t="inlineStr"/>
@@ -75277,12 +75277,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>310672</t>
+          <t>310694</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
+          <t>4.784 - SEKAPISO METALURGICA LTDA</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -75290,22 +75290,22 @@
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>116.922</t>
+          <t>52.924</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H270" s="2" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="I270" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -75314,7 +75314,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>8562.49</t>
+          <t>2200.8</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -75324,12 +75324,12 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>7991.52</t>
+          <t>2200.8</t>
         </is>
       </c>
       <c r="P270" t="inlineStr">
@@ -75339,12 +75339,12 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>0.049824</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -75354,7 +75354,7 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>8.562,49</t>
+          <t>2.200,80</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
@@ -75364,12 +75364,12 @@
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>6962.21</t>
+          <t>2200.8</t>
         </is>
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="X270" t="inlineStr">
@@ -75379,12 +75379,12 @@
       </c>
       <c r="Y270" t="inlineStr">
         <is>
-          <t>62.66</t>
+          <t>19.76</t>
         </is>
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>54.13</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -75399,17 +75399,17 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>570.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
         <is>
-          <t>7991.52</t>
+          <t>2200.8</t>
         </is>
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>319.66</t>
+          <t>154.05</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -75536,7 +75536,7 @@
       <c r="BM270" t="inlineStr"/>
       <c r="BN270" t="inlineStr">
         <is>
-          <t>42260735635346000140550020001169221345408115</t>
+          <t>35260760225604000168550030000529241643007196</t>
         </is>
       </c>
       <c r="BO270" t="inlineStr"/>
@@ -75555,7 +75555,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>310694</t>
+          <t>310697</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -75568,7 +75568,7 @@
       <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
-          <t>52.924</t>
+          <t>52.923</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -75592,7 +75592,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2200.8</t>
+          <t>336.03</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -75602,12 +75602,12 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>2200.8</t>
+          <t>336.03</t>
         </is>
       </c>
       <c r="P271" t="inlineStr">
@@ -75632,7 +75632,7 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>2.200,80</t>
+          <t>336,03</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
@@ -75642,12 +75642,12 @@
       </c>
       <c r="V271" t="inlineStr">
         <is>
-          <t>2200.8</t>
+          <t>336.03</t>
         </is>
       </c>
       <c r="W271" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X271" t="inlineStr">
@@ -75657,12 +75657,12 @@
       </c>
       <c r="Y271" t="inlineStr">
         <is>
-          <t>19.76</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -75682,12 +75682,12 @@
       </c>
       <c r="AD271" t="inlineStr">
         <is>
-          <t>2200.8</t>
+          <t>336.03</t>
         </is>
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>154.05</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -75814,7 +75814,7 @@
       <c r="BM271" t="inlineStr"/>
       <c r="BN271" t="inlineStr">
         <is>
-          <t>35260760225604000168550030000529241643007196</t>
+          <t>35260760225604000168550030000529231962967378</t>
         </is>
       </c>
       <c r="BO271" t="inlineStr"/>
@@ -75825,284 +75825,6 @@
         </is>
       </c>
       <c r="BR271" t="inlineStr">
-        <is>
-          <t>sr acabamentos</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>310697</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>4.784 - SEKAPISO METALURGICA LTDA</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>52.923</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H272" s="2" t="n">
-        <v>46211</v>
-      </c>
-      <c r="I272" s="2" t="n">
-        <v>46212</v>
-      </c>
-      <c r="J272" s="2" t="n">
-        <v>46239</v>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>XML</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>336.03</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O272" t="inlineStr">
-        <is>
-          <t>336.03</t>
-        </is>
-      </c>
-      <c r="P272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T272" t="inlineStr">
-        <is>
-          <t>336,03</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>Ag. chegada da mercadoria</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>336.03</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>1 - OBJETIVA</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>336.03</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>23.53</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AO272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
-      <c r="AT272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AU272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AV272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AW272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AX272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AY272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="AZ272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="BA272" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="BB272" t="inlineStr">
-        <is>
-          <t>2.102</t>
-        </is>
-      </c>
-      <c r="BC272" t="inlineStr"/>
-      <c r="BD272" t="inlineStr"/>
-      <c r="BE272" t="inlineStr"/>
-      <c r="BF272" t="inlineStr"/>
-      <c r="BG272" t="inlineStr"/>
-      <c r="BH272" t="inlineStr"/>
-      <c r="BI272" t="inlineStr"/>
-      <c r="BJ272" t="inlineStr"/>
-      <c r="BK272" t="inlineStr"/>
-      <c r="BL272" t="inlineStr"/>
-      <c r="BM272" t="inlineStr"/>
-      <c r="BN272" t="inlineStr">
-        <is>
-          <t>35260760225604000168550030000529231962967378</t>
-        </is>
-      </c>
-      <c r="BO272" t="inlineStr"/>
-      <c r="BP272" t="inlineStr"/>
-      <c r="BQ272" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="BR272" t="inlineStr">
         <is>
           <t>sr acabamentos</t>
         </is>
